--- a/artfynd/A 54156-2019 artfynd.xlsx
+++ b/artfynd/A 54156-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 54156-2019 artfynd.xlsx
+++ b/artfynd/A 54156-2019 artfynd.xlsx
@@ -2615,7 +2615,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">

--- a/artfynd/A 54156-2019 artfynd.xlsx
+++ b/artfynd/A 54156-2019 artfynd.xlsx
@@ -3636,7 +3636,7 @@
         <v>122768784</v>
       </c>
       <c r="B25" t="n">
-        <v>57497</v>
+        <v>57500</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>

--- a/artfynd/A 54156-2019 artfynd.xlsx
+++ b/artfynd/A 54156-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3749,6 +3749,120 @@
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>123506896</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57815</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>103008</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Ärtsångare</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Curruca curruca</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Marielund, Ålefors, Sm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>537751</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6354686</v>
+      </c>
+      <c r="S26" t="n">
+        <v>50</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Virserum</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Marie Lundberg</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Marie Lundberg</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54156-2019 artfynd.xlsx
+++ b/artfynd/A 54156-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3863,6 +3863,124 @@
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>124970949</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57529</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Blackelid, Ålefors, Sm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>537742</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6354661</v>
+      </c>
+      <c r="S27" t="n">
+        <v>50</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Virserum</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Marie Lundberg</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Marie Lundberg</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54156-2019 artfynd.xlsx
+++ b/artfynd/A 54156-2019 artfynd.xlsx
@@ -3906,7 +3906,7 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">

--- a/artfynd/A 54156-2019 artfynd.xlsx
+++ b/artfynd/A 54156-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3981,6 +3981,124 @@
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>125457950</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57761</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Blackelid, Ålefors, Sm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>537864</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6354744</v>
+      </c>
+      <c r="S28" t="n">
+        <v>50</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Virserum</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-05-27</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Marie Lundberg</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Marie Lundberg</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54156-2019 artfynd.xlsx
+++ b/artfynd/A 54156-2019 artfynd.xlsx
@@ -3868,7 +3868,7 @@
         <v>124970949</v>
       </c>
       <c r="B27" t="n">
-        <v>57529</v>
+        <v>57632</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3986,7 +3986,7 @@
         <v>125457950</v>
       </c>
       <c r="B28" t="n">
-        <v>57761</v>
+        <v>57914</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>

--- a/artfynd/A 54156-2019 artfynd.xlsx
+++ b/artfynd/A 54156-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3868,12 +3868,7 @@
         <v>124970949</v>
       </c>
       <c r="B27" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3986,12 +3981,7 @@
         <v>125457950</v>
       </c>
       <c r="B28" t="n">
-        <v>57914</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57932</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4098,6 +4088,232 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>125746829</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57932</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Mitten, Ålefors, Sm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>537688</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6354702</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Virserum</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Marie Lundberg</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Marie Lundberg</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>125804440</v>
+      </c>
+      <c r="B30" t="n">
+        <v>58019</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Mitten, Ålefors, Sm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>537678</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6354713</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Virserum</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Marie Lundberg</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Marie Lundberg</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 54156-2019 artfynd.xlsx
+++ b/artfynd/A 54156-2019 artfynd.xlsx
@@ -2738,12 +2738,7 @@
         <v>99540782</v>
       </c>
       <c r="B18" t="n">
-        <v>56717</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57979</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2791,10 +2786,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>537790.5872411492</v>
+        <v>537791</v>
       </c>
       <c r="R18" t="n">
-        <v>6354694.630716937</v>
+        <v>6354694</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2824,19 +2819,9 @@
           <t>2022-03-28</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2022-03-28</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2998,12 +2983,7 @@
         <v>99991140</v>
       </c>
       <c r="B20" t="n">
-        <v>56717</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57979</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3051,10 +3031,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>537726.9167421204</v>
+        <v>537727</v>
       </c>
       <c r="R20" t="n">
-        <v>6354678.390081504</v>
+        <v>6354678</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -3084,19 +3064,9 @@
           <t>2022-04-17</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2022-04-17</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 54156-2019 artfynd.xlsx
+++ b/artfynd/A 54156-2019 artfynd.xlsx
@@ -2738,7 +2738,7 @@
         <v>99540782</v>
       </c>
       <c r="B18" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2983,7 +2983,7 @@
         <v>99991140</v>
       </c>
       <c r="B20" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -4177,7 +4177,7 @@
         <v>125804440</v>
       </c>
       <c r="B30" t="n">
-        <v>58019</v>
+        <v>58020</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 54156-2019 artfynd.xlsx
+++ b/artfynd/A 54156-2019 artfynd.xlsx
@@ -3951,7 +3951,7 @@
         <v>125457950</v>
       </c>
       <c r="B28" t="n">
-        <v>57932</v>
+        <v>57933</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         <v>125746829</v>
       </c>
       <c r="B29" t="n">
-        <v>57932</v>
+        <v>57933</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 54156-2019 artfynd.xlsx
+++ b/artfynd/A 54156-2019 artfynd.xlsx
@@ -2738,7 +2738,7 @@
         <v>99540782</v>
       </c>
       <c r="B18" t="n">
-        <v>57980</v>
+        <v>57981</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2983,7 +2983,7 @@
         <v>99991140</v>
       </c>
       <c r="B20" t="n">
-        <v>57980</v>
+        <v>57981</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>125457950</v>
       </c>
       <c r="B28" t="n">
-        <v>57933</v>
+        <v>57934</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         <v>125746829</v>
       </c>
       <c r="B29" t="n">
-        <v>57933</v>
+        <v>57934</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4177,7 +4177,7 @@
         <v>125804440</v>
       </c>
       <c r="B30" t="n">
-        <v>58020</v>
+        <v>58021</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 54156-2019 artfynd.xlsx
+++ b/artfynd/A 54156-2019 artfynd.xlsx
@@ -2738,7 +2738,7 @@
         <v>99540782</v>
       </c>
       <c r="B18" t="n">
-        <v>57981</v>
+        <v>57985</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2983,7 +2983,7 @@
         <v>99991140</v>
       </c>
       <c r="B20" t="n">
-        <v>57981</v>
+        <v>57985</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         <v>125746829</v>
       </c>
       <c r="B29" t="n">
-        <v>57934</v>
+        <v>57938</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4177,7 +4177,7 @@
         <v>125804440</v>
       </c>
       <c r="B30" t="n">
-        <v>58021</v>
+        <v>58025</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 54156-2019 artfynd.xlsx
+++ b/artfynd/A 54156-2019 artfynd.xlsx
@@ -2738,7 +2738,7 @@
         <v>99540782</v>
       </c>
       <c r="B18" t="n">
-        <v>57985</v>
+        <v>57987</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2983,7 +2983,7 @@
         <v>99991140</v>
       </c>
       <c r="B20" t="n">
-        <v>57985</v>
+        <v>57987</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -4177,7 +4177,7 @@
         <v>125804440</v>
       </c>
       <c r="B30" t="n">
-        <v>58025</v>
+        <v>58027</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
